--- a/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
@@ -14956,7 +14956,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -23927,7 +23927,7 @@
           <t>E | 486呎 (2房)
 $1,018万
 $20,951/呎
-(25年-03月)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G22" s="18" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -20760,4262 +20617,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海盈山第4A期 - 2A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>215 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>185 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1592呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1478呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 658呎 (3房)
-$2,042万
-$31,027/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 616呎 (2房)
-$1,817万
-$29,491/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 570呎 (2房)
-$1,725万
-$30,261/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 581呎 (2房)
-$1,391万
-$23,946/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,062万
-$20,870/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 658呎 (3房)
-$2,010万
-$30,550/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 616呎 (2房)
-$1,788万
-$29,028/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,701万
-$29,792/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,289万
-$22,154/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,048万
-$20,580/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr"/>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 658呎 (3房)
-$1,999万
-$30,381/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 616呎 (2房)
-$1,778万
-$28,857/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,694万
-$29,674/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,284万
-$22,065/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,043万
-$20,498/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-$3,444万
-$40,375/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr"/>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,988万
-$30,161/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 616呎 (2房)
-$1,766万
-$28,662/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,796万
-$31,450/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,279万
-$25,329/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,039万
-$20,418/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 658呎 (3房)
-$1,988万
-$30,207/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 616呎 (2房)
-$1,766万
-$28,662/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,680万
-$29,425/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,279万
-$21,978/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,039万
-$20,418/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr"/>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$2,074万
-$31,378/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,715万
-$27,981/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,667万
-$29,193/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,269万
-$21,804/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,031万
-$20,256/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-$3,246万
-$38,060/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr"/>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$1,948万
-$29,469/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,689万
-$27,561/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,660万
-$29,076/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,264万
-$21,715/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,053万
-$20,692/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-$3,030万
-$35,518/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr"/>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$1,889万
-$28,571/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,680万
-$27,399/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 570呎 (2房)
-$1,654万
-$29,012/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,259万
-$21,628/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,049万
-$20,608/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-$3,009万
-$35,271/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr"/>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$1,878万
-$28,413/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,670万
-$27,236/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,647万
-$28,845/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,254万
-$21,544/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,019万
-$20,012/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-$2,988万
-$35,026/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr"/>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$1,868万
-$28,254/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,669万
-$27,228/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,640万
-$28,730/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,249万
-$21,458/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,015万
-$19,934/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-$3,182万
-$37,300/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr"/>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$1,857万
-$28,097/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,659万
-$27,067/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,634万
-$28,615/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,244万
-$21,372/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,011万
-$19,854/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-$3,224万
-$37,801/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr"/>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$1,847万
-$27,940/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,649万
-$26,908/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,627万
-$28,502/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,239万
-$21,287/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,007万
-$19,776/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-$3,199万
-$37,501/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr"/>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$1,954万
-$29,565/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,640万
-$26,749/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,651万
-$28,908/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,234万
-$21,202/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,003万
-$19,696/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr"/>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$1,837万
-$27,784/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,640万
-$26,749/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1,621万
-$28,388/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,234万
-$21,202/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1,003万
-$19,696/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr"/>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$1,817万
-$27,492/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,622万
-$26,460/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 570呎 (2房)
-$1,615万
-$28,336/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,303万
-$22,383/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$995万
-$19,540/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr"/>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 661呎 (3房)
-$1,807万
-$27,339/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 613呎 (2房)
-$1,612万
-$26,305/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 570呎 (2房)
-$1,609万
-$28,224/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,297万
-$22,293/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$991万
-$19,463/呎
-(25年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,428万
-$27,615/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,450万
-$27,881/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,571万
-$23,840/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,371万
-$22,186/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,540万
-$27,114/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,214万
-$20,867/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,261万
-$31,288/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,356万
-$26,226/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,444万
-$27,770/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,560万
-$23,675/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,362万
-$22,043/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,534万
-$27,005/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,210万
-$20,783/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,080万
-$26,788/呎
-(23年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,416万
-$27,395/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,371万
-$26,372/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,549万
-$23,510/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,353万
-$21,899/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-$1,556万
-$27,439/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,205万
-$20,701/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,250万
-$31,007/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,345万
-$26,016/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,366万
-$26,267/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,539万
-$23,347/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,345万
-$21,758/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,522万
-$26,790/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,200万
-$20,619/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,244万
-$30,868/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,340万
-$25,912/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 518呎 (2房)
-$1,360万
-$26,264/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,528万
-$23,185/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,336万
-$21,618/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,516万
-$26,683/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,195万
-$20,537/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,238万
-$30,730/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,561万
-$30,193/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,360万
-$26,163/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,528万
-$23,185/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,370万
-$22,172/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,516万
-$26,683/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,195万
-$20,537/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,238万
-$30,730/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,329万
-$25,707/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,350万
-$25,955/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,507万
-$22,865/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,319万
-$21,340/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,504万
-$26,471/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,186万
-$20,375/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,227万
-$30,454/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,324万
-$25,604/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,344万
-$25,851/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,496万
-$22,707/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,310万
-$21,203/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,498万
-$26,366/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,181万
-$20,293/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,222万
-$30,318/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,318万
-$25,503/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,339万
-$25,748/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,486万
-$22,549/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,302万
-$21,065/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-$1,492万
-$26,307/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,176万
-$20,213/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,216万
-$30,181/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,313万
-$25,399/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,334万
-$25,646/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,476万
-$22,392/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,293万
-$20,929/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,486万
-$26,156/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,172万
-$20,133/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,211万
-$30,047/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,308万
-$25,300/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,328万
-$25,543/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,465万
-$22,237/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,285万
-$20,794/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,480万
-$26,052/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,167万
-$20,052/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H33" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,206万
-$29,913/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,303万
-$25,198/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,323万
-$25,442/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,455万
-$22,083/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,277万
-$20,659/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,474万
-$25,948/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,162万
-$19,972/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,200万
-$29,779/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,298万
-$25,098/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,382万
-$26,576/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,445万
-$21,928/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,269万
-$20,526/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-$1,603万
-$28,273/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,158万
-$19,891/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H35" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,195万
-$29,645/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,298万
-$25,098/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,318万
-$25,340/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,445万
-$21,928/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,269万
-$20,526/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,468万
-$25,845/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,158万
-$19,891/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,195万
-$29,645/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,287万
-$24,898/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,371万
-$26,364/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,425万
-$21,625/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,284万
-$20,782/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-$1,590万
-$28,049/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>F | 581呎 (2房)
-$1,148万
-$19,767/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H37" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,184万
-$29,382/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>A | 517呎 (2房)
-$1,282万
-$24,800/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1,302万
-$25,038/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1,415万
-$21,474/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 618呎 (2房)
-$1,244万
-$20,132/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>E | 568呎 (2房)
-$1,451万
-$25,538/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1,144万
-$19,654/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H38" s="20" t="inlineStr">
-        <is>
-          <t>G | 403呎 (1房)
-$1,179万
-$29,253/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 479呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>B | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>C | 622呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>D | 594呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr"/>
-      <c r="G39" s="17" t="inlineStr"/>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>G | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海盈山第4A期 - 2B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>217 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>175 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>33 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1847呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1218呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,653万
-$39,919/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,219万
-$32,722/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$3,547万
-$41,201/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,231万
-$23,014/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,092万
-$22,468/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,119万
-$22,160/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,561万
-$38,919/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,182万
-$32,176/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$3,033万
-$35,226/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,214万
-$22,696/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 485呎 (2房)
-$1,077万
-$22,202/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,104万
-$21,852/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,470万
-$37,919/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,166万
-$31,951/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$3,010万
-$34,965/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,209万
-$22,605/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,073万
-$22,070/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,099万
-$21,764/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,378万
-$36,919/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,151万
-$31,729/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$2,869万
-$33,321/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,205万
-$22,515/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,068万
-$21,980/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,095万
-$21,678/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,378万
-$36,919/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,151万
-$31,729/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$2,869万
-$33,321/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,205万
-$22,515/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,068万
-$21,980/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,095万
-$21,678/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,295万
-$36,011/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,122万
-$31,291/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$2,923万
-$33,951/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,195万
-$22,337/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,060万
-$21,805/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,086万
-$21,507/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,411万
-$37,279/呎
-(23年-12月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,138万
-$31,538/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$2,843万
-$33,021/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,190万
-$22,248/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 485呎 (2房)
-$1,056万
-$21,763/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,082万
-$21,422/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,388万
-$37,027/呎
-(23年-09月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,085万
-$30,757/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$2,883万
-$33,482/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,186万
-$22,161/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,051万
-$21,633/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,077万
-$21,335/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,180万
-$34,754/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,071万
-$30,543/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$2,863万
-$33,249/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,181万
-$22,072/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,047万
-$21,546/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,073万
-$21,250/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,157万
-$34,503/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,056万
-$30,332/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$2,843万
-$33,017/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,176万
-$21,984/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,043万
-$21,461/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,069万
-$21,164/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,134万
-$34,251/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,042万
-$30,121/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$2,998万
-$34,816/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,171万
-$21,896/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,039万
-$21,375/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,065万
-$21,080/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,111万
-$34,000/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,127万
-$31,372/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$3,080万
-$35,776/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,167万
-$21,810/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,035万
-$21,290/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,060万
-$20,997/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,088万
-$33,749/呎
-(23年-10月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$2,051万
-$30,249/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$3,059万
-$35,533/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,162万
-$21,722/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,031万
-$21,205/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,056万
-$20,913/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,065万
-$33,497/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$1,994万
-$29,410/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,162万
-$21,722/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,031万
-$21,205/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,056万
-$20,913/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,088万
-$33,746/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$1,942万
-$28,641/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,153万
-$21,550/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,022万
-$21,036/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,048万
-$20,748/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 915呎 (3房)
-$3,065万
-$33,495/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 678呎 (2房)
-$1,904万
-$28,080/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 861呎 (3房)
-$3,014万
-$35,000/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,148万
-$21,464/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 486呎 (2房)
-$1,018万
-$20,951/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,044万
-$20,665/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$3,027万
-$33,120/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,882万
-$27,681/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,452万
-$23,086/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,144万
-$21,376/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,014万
-$20,782/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$3,044万
-$33,299/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,907万
-$28,048/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,445万
-$22,971/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,139万
-$21,292/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,010万
-$20,700/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$3,075万
-$33,639/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,955万
-$28,743/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,438万
-$22,856/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,135万
-$21,207/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,006万
-$20,616/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$3,053万
-$33,405/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,854万
-$27,270/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,431万
-$22,743/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,130万
-$21,123/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$1,002万
-$20,536/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-$1,056万
-$26,810/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,891万
-$31,630/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,879万
-$27,630/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,423万
-$22,629/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,126万
-$21,038/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$998万
-$20,453/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-$1,282万
-$32,548/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,891万
-$31,630/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,845万
-$27,134/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,423万
-$22,629/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,126万
-$21,038/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$998万
-$20,453/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-$1,282万
-$32,548/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,903万
-$31,764/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,827万
-$26,865/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,409万
-$22,406/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,117万
-$20,872/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$990万
-$20,293/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G29" s="20" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-$1,271万
-$32,259/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,883万
-$31,544/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,818万
-$26,731/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,402万
-$22,294/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,112万
-$20,789/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$986万
-$20,210/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G30" s="20" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-$1,265万
-$32,112/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$3,288万
-$35,974/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,897万
-$27,896/呎
-(23年-10月)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,395万
-$22,184/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,108万
-$20,706/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$982万
-$20,130/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G31" s="20" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-$1,260万
-$31,970/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,928万
-$32,037/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,888万
-$27,758/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,388万
-$22,073/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,103万
-$20,624/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$978万
-$20,047/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-$1,254万
-$31,827/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,908万
-$31,815/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,878万
-$27,620/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,381万
-$21,963/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,099万
-$20,541/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$974万
-$19,968/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-$1,248万
-$31,685/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,753万
-$30,124/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,782万
-$26,204/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,375万
-$21,854/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,094万
-$20,458/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$971万
-$19,890/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,868万
-$31,374/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,860万
-$27,346/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,368万
-$21,746/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,090万
-$20,378/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$967万
-$19,810/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,762万
-$30,216/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,805万
-$26,551/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,368万
-$21,746/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,090万
-$20,378/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$967万
-$19,810/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,762万
-$30,216/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,788万
-$26,288/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,354万
-$21,530/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,082万
-$20,216/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$959万
-$19,652/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>A | 914呎 (3房)
-$2,678万
-$29,298/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>B | 680呎 (2房)
-$1,747万
-$25,688/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 629呎 (2房)
-$1,347万
-$21,422/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 535呎 (2房)
-$1,077万
-$20,136/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>E | 488呎 (2房)
-$955万
-$19,574/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>F | 394呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>G | 389呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 866呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>B | 643呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>D | 498呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>E | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>F | 357呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>G | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +154,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +235,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +671,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -20617,4 +20814,4262 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1592呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1478呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 658呎 (3房)
+$2042万
+$31,027/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 616呎 (2房)
+$1817万
+$29,491/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 570呎 (2房)
+$1725万
+$30,261/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 581呎 (2房)
+$1391万
+$23,946/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1062万
+$20,870/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 658呎 (3房)
+$2010万
+$30,550/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 616呎 (2房)
+$1788万
+$29,028/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1701万
+$29,792/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1289万
+$22,154/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1048万
+$20,580/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 658呎 (3房)
+$1999万
+$30,381/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 616呎 (2房)
+$1778万
+$28,857/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1694万
+$29,674/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1284万
+$22,065/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1043万
+$20,498/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+$3444万
+$40,375/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1988万
+$30,161/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 616呎 (2房)
+$1766万
+$28,662/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1796万
+$31,450/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1279万
+$25,329/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1039万
+$20,418/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 658呎 (3房)
+$1988万
+$30,207/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 616呎 (2房)
+$1766万
+$28,662/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1680万
+$29,425/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1279万
+$21,978/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1039万
+$20,418/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr"/>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$2074万
+$31,378/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1715万
+$27,981/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1667万
+$29,193/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1269万
+$21,804/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1031万
+$20,256/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+$3246万
+$38,060/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr"/>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$1948万
+$29,469/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1689万
+$27,561/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1660万
+$29,076/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1264万
+$21,715/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1053万
+$20,692/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+$3030万
+$35,518/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr"/>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$1889万
+$28,571/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1680万
+$27,399/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 570呎 (2房)
+$1654万
+$29,012/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1259万
+$21,628/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1049万
+$20,608/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+$3009万
+$35,271/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr"/>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$1878万
+$28,413/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1670万
+$27,236/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1647万
+$28,845/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1254万
+$21,544/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1019万
+$20,012/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+$2988万
+$35,026/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr"/>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$1868万
+$28,254/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1669万
+$27,228/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1640万
+$28,730/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1249万
+$21,458/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1015万
+$19,934/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+$3182万
+$37,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr"/>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$1857万
+$28,097/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1659万
+$27,067/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1634万
+$28,615/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1244万
+$21,372/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1011万
+$19,854/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+$3224万
+$37,801/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr"/>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$1847万
+$27,940/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1649万
+$26,908/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1627万
+$28,502/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1239万
+$21,287/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1007万
+$19,776/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+$3199万
+$37,501/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr"/>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$1954万
+$29,565/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1640万
+$26,749/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1651万
+$28,908/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1234万
+$21,202/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1003万
+$19,696/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr"/>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$1837万
+$27,784/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1640万
+$26,749/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1621万
+$28,388/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1234万
+$21,202/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1003万
+$19,696/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr"/>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$1817万
+$27,492/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1622万
+$26,460/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 570呎 (2房)
+$1615万
+$28,336/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1303万
+$22,383/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$995万
+$19,540/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr"/>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 661呎 (3房)
+$1807万
+$27,339/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 613呎 (2房)
+$1612万
+$26,305/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 570呎 (2房)
+$1609万
+$28,224/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1297万
+$22,293/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$991万
+$19,463/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1428万
+$27,615/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1450万
+$27,881/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1571万
+$23,840/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1371万
+$22,186/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1540万
+$27,114/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1214万
+$20,867/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1261万
+$31,288/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1356万
+$26,226/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1444万
+$27,770/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1560万
+$23,675/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1362万
+$22,043/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1534万
+$27,005/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1210万
+$20,783/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1080万
+$26,788/呎
+(23年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1416万
+$27,395/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1371万
+$26,372/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1549万
+$23,510/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1353万
+$21,899/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+$1556万
+$27,439/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1205万
+$20,701/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1250万
+$31,007/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1345万
+$26,016/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1366万
+$26,267/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1539万
+$23,347/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1345万
+$21,758/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1522万
+$26,790/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1200万
+$20,619/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1244万
+$30,868/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1340万
+$25,912/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 518呎 (2房)
+$1360万
+$26,264/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1528万
+$23,185/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1336万
+$21,618/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1516万
+$26,683/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1195万
+$20,537/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1238万
+$30,730/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1561万
+$30,193/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1360万
+$26,163/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1528万
+$23,185/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1370万
+$22,172/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1516万
+$26,683/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1195万
+$20,537/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1238万
+$30,730/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1329万
+$25,707/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1350万
+$25,955/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1507万
+$22,865/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1319万
+$21,340/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1504万
+$26,471/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1186万
+$20,375/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1227万
+$30,454/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1324万
+$25,604/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1344万
+$25,851/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1496万
+$22,707/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1310万
+$21,203/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1498万
+$26,366/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1181万
+$20,293/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1222万
+$30,318/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1318万
+$25,503/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1339万
+$25,748/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1486万
+$22,549/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1302万
+$21,065/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+$1492万
+$26,307/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1176万
+$20,213/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1216万
+$30,181/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1313万
+$25,399/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1334万
+$25,646/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1476万
+$22,392/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1293万
+$20,929/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1486万
+$26,156/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1172万
+$20,133/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1211万
+$30,047/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1308万
+$25,300/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1328万
+$25,543/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1465万
+$22,237/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1285万
+$20,794/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1480万
+$26,052/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1167万
+$20,052/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1206万
+$29,913/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1303万
+$25,198/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1323万
+$25,442/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1455万
+$22,083/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1277万
+$20,659/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1474万
+$25,948/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1162万
+$19,972/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1200万
+$29,779/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1298万
+$25,098/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1382万
+$26,576/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1445万
+$21,928/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1269万
+$20,526/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+$1603万
+$28,273/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1158万
+$19,891/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1195万
+$29,645/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1298万
+$25,098/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1318万
+$25,340/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1445万
+$21,928/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1269万
+$20,526/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1468万
+$25,845/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1158万
+$19,891/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1195万
+$29,645/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1287万
+$24,898/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1371万
+$26,364/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1425万
+$21,625/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1284万
+$20,782/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+$1590万
+$28,049/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>F | 581呎 (2房)
+$1148万
+$19,767/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1184万
+$29,382/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>A | 517呎 (2房)
+$1282万
+$24,800/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1302万
+$25,038/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1415万
+$21,474/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 618呎 (2房)
+$1244万
+$20,132/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 568呎 (2房)
+$1451万
+$25,538/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1144万
+$19,654/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>G | 403呎 (1房)
+$1179万
+$29,253/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 479呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 622呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 594呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr"/>
+      <c r="G38" s="21" t="inlineStr"/>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>G | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1847呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1218呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3653万
+$39,919/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2219万
+$32,722/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$3547万
+$41,201/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1231万
+$23,014/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1092万
+$22,468/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1119万
+$22,160/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3561万
+$38,919/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2182万
+$32,176/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$3033万
+$35,226/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1214万
+$22,696/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 485呎 (2房)
+$1077万
+$22,202/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1104万
+$21,852/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3470万
+$37,919/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2166万
+$31,951/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$3010万
+$34,965/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1209万
+$22,605/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1073万
+$22,070/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1099万
+$21,764/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3378万
+$36,919/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2151万
+$31,729/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$2869万
+$33,321/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1205万
+$22,515/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1068万
+$21,980/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1095万
+$21,678/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3378万
+$36,919/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2151万
+$31,729/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$2869万
+$33,321/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1205万
+$22,515/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1068万
+$21,980/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1095万
+$21,678/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3295万
+$36,011/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2122万
+$31,291/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$2923万
+$33,951/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1195万
+$22,337/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1060万
+$21,805/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1086万
+$21,507/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3411万
+$37,279/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2138万
+$31,538/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$2843万
+$33,021/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1190万
+$22,248/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 485呎 (2房)
+$1056万
+$21,763/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1082万
+$21,422/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3388万
+$37,027/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2085万
+$30,757/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$2883万
+$33,482/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1186万
+$22,161/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1051万
+$21,633/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1077万
+$21,335/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3180万
+$34,754/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2071万
+$30,543/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$2863万
+$33,249/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1181万
+$22,072/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1047万
+$21,546/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1073万
+$21,250/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3157万
+$34,503/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2056万
+$30,332/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$2843万
+$33,017/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1176万
+$21,984/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1043万
+$21,461/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1069万
+$21,164/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3134万
+$34,251/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2042万
+$30,121/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$2998万
+$34,816/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1171万
+$21,896/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1039万
+$21,375/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1065万
+$21,080/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3111万
+$34,000/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2127万
+$31,372/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$3080万
+$35,776/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1167万
+$21,810/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1035万
+$21,290/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1060万
+$20,997/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3088万
+$33,749/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$2051万
+$30,249/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$3059万
+$35,533/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1162万
+$21,722/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1031万
+$21,205/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1056万
+$20,913/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3065万
+$33,497/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$1994万
+$29,410/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1162万
+$21,722/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1031万
+$21,205/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1056万
+$20,913/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3088万
+$33,746/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$1942万
+$28,641/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1153万
+$21,550/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1022万
+$21,036/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1048万
+$20,748/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 915呎 (3房)
+$3065万
+$33,495/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 678呎 (2房)
+$1904万
+$28,080/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 861呎 (3房)
+$3014万
+$35,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1148万
+$21,464/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 486呎 (2房)
+$1018万
+$20,951/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1044万
+$20,665/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$3027万
+$33,120/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1882万
+$27,681/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1452万
+$23,086/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1144万
+$21,376/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1014万
+$20,782/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$3044万
+$33,299/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1907万
+$28,048/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1445万
+$22,971/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1139万
+$21,292/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1010万
+$20,700/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$3075万
+$33,639/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1955万
+$28,743/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1438万
+$22,856/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1135万
+$21,207/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1006万
+$20,616/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$3053万
+$33,405/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1854万
+$27,270/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1431万
+$22,743/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1130万
+$21,123/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$1002万
+$20,536/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+$1056万
+$26,810/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2891万
+$31,630/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1879万
+$27,630/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1423万
+$22,629/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1126万
+$21,038/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$998万
+$20,453/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+$1282万
+$32,548/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2891万
+$31,630/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1845万
+$27,134/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1423万
+$22,629/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1126万
+$21,038/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$998万
+$20,453/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+$1282万
+$32,548/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2903万
+$31,764/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1827万
+$26,865/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1409万
+$22,406/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1117万
+$20,872/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$990万
+$20,293/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+$1271万
+$32,259/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2883万
+$31,544/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1818万
+$26,731/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1402万
+$22,294/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1112万
+$20,789/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$986万
+$20,210/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+$1265万
+$32,112/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$3288万
+$35,974/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1897万
+$27,896/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1395万
+$22,184/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1108万
+$20,706/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$982万
+$20,130/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+$1260万
+$31,970/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2928万
+$32,037/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1888万
+$27,758/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1388万
+$22,073/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1103万
+$20,624/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$978万
+$20,047/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+$1254万
+$31,827/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2908万
+$31,815/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1878万
+$27,620/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1381万
+$21,963/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1099万
+$20,541/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$974万
+$19,968/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+$1248万
+$31,685/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2753万
+$30,124/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1782万
+$26,204/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1375万
+$21,854/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1094万
+$20,458/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$971万
+$19,890/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2868万
+$31,374/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1860万
+$27,346/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1368万
+$21,746/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1090万
+$20,378/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$967万
+$19,810/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2762万
+$30,216/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1805万
+$26,551/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1368万
+$21,746/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1090万
+$20,378/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$967万
+$19,810/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2762万
+$30,216/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1788万
+$26,288/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1354万
+$21,530/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1082万
+$20,216/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$959万
+$19,652/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>A | 914呎 (3房)
+$2678万
+$29,298/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B | 680呎 (2房)
+$1747万
+$25,688/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 629呎 (2房)
+$1347万
+$21,422/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 535呎 (2房)
+$1077万
+$20,136/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 488呎 (2房)
+$955万
+$19,574/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>F | 394呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>G | 389呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 866呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 643呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 498呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>E | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>F | 357呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>G | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
@@ -671,7 +671,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
@@ -6957,18 +6957,18 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K101" s="5" t="n">
-        <v>9835020</v>
+        <v>10339380</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>24405</v>
+        <v>25656</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -7825,18 +7825,18 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K115" s="5" t="n">
-        <v>9746880</v>
+        <v>10246720</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>24186</v>
+        <v>25426</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
@@ -8259,18 +8259,18 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K122" s="5" t="n">
-        <v>9703200</v>
+        <v>10200800</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>24077</v>
+        <v>25312</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N122" s="3" t="inlineStr">
@@ -8693,18 +8693,18 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K129" s="5" t="n">
-        <v>9659520</v>
+        <v>10154880</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>23969</v>
+        <v>25198</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
@@ -9127,18 +9127,18 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K136" s="5" t="n">
-        <v>9659520</v>
+        <v>10154880</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>23969</v>
+        <v>25198</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N136" s="3" t="inlineStr">
@@ -9561,18 +9561,18 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>9572940</v>
+        <v>10063860</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>23754</v>
+        <v>24972</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N143" s="3" t="inlineStr">
@@ -9995,18 +9995,18 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
-        <v>9530040</v>
+        <v>10018760</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>23648</v>
+        <v>24860</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -10429,18 +10429,18 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K157" s="5" t="n">
-        <v>9487140</v>
+        <v>9973660</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>23541</v>
+        <v>24749</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
@@ -10863,18 +10863,18 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K164" s="5" t="n">
-        <v>9445020</v>
+        <v>9929380</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>23437</v>
+        <v>24639</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N164" s="3" t="inlineStr">
@@ -11297,18 +11297,18 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K171" s="5" t="n">
-        <v>9402900</v>
+        <v>9885100</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>23332</v>
+        <v>24529</v>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr">
@@ -11731,18 +11731,18 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>9360780</v>
+        <v>9840820</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>23228</v>
+        <v>24419</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12165,18 +12165,18 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K185" s="5" t="n">
-        <v>9318660</v>
+        <v>9796540</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>23123</v>
+        <v>24309</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N185" s="3" t="inlineStr">
@@ -12599,18 +12599,18 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K192" s="5" t="n">
-        <v>9318660</v>
+        <v>9796540</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>23123</v>
+        <v>24309</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N192" s="3" t="inlineStr">
@@ -13033,18 +13033,18 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K199" s="5" t="n">
-        <v>9235980</v>
+        <v>9709620</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>22918</v>
+        <v>24093</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N199" s="3" t="inlineStr">
@@ -13467,18 +13467,18 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K206" s="5" t="n">
-        <v>9195420</v>
+        <v>9666980</v>
       </c>
       <c r="L206" s="5" t="n">
-        <v>22817</v>
+        <v>23988</v>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
@@ -22221,18 +22221,18 @@
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K345" s="5" t="n">
-        <v>10002720</v>
+        <v>10515680</v>
       </c>
       <c r="L345" s="5" t="n">
-        <v>25388</v>
+        <v>26690</v>
       </c>
       <c r="M345" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N345" s="3" t="inlineStr">
@@ -22663,18 +22663,18 @@
       </c>
       <c r="J352" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K352" s="5" t="n">
-        <v>10002720</v>
+        <v>10515680</v>
       </c>
       <c r="L352" s="5" t="n">
-        <v>25388</v>
+        <v>26690</v>
       </c>
       <c r="M352" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N352" s="3" t="inlineStr">
@@ -23105,18 +23105,18 @@
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>9913800</v>
+        <v>10422200</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>25162</v>
+        <v>26452</v>
       </c>
       <c r="M359" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N359" s="3" t="inlineStr">
@@ -23547,18 +23547,18 @@
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K366" s="5" t="n">
-        <v>9868560</v>
+        <v>10374640</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>25047</v>
+        <v>26332</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N366" s="3" t="inlineStr">
@@ -23989,18 +23989,18 @@
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K373" s="5" t="n">
-        <v>9824880</v>
+        <v>10328720</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>24936</v>
+        <v>26215</v>
       </c>
       <c r="M373" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N373" s="3" t="inlineStr">
@@ -24431,18 +24431,18 @@
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K380" s="5" t="n">
-        <v>9781200</v>
+        <v>10282800</v>
       </c>
       <c r="L380" s="5" t="n">
-        <v>24825</v>
+        <v>26098</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N380" s="3" t="inlineStr">
@@ -24873,18 +24873,18 @@
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K387" s="5" t="n">
-        <v>9737520</v>
+        <v>10236880</v>
       </c>
       <c r="L387" s="5" t="n">
-        <v>24715</v>
+        <v>25982</v>
       </c>
       <c r="M387" s="3" t="inlineStr">
         <is>
-          <t>120 置靈活付款計劃</t>
+          <t>270靈活現金付款計劃</t>
         </is>
       </c>
       <c r="N387" s="3" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
@@ -28132,7 +28132,7 @@
           <t>C | 658呎 (3房)
 $2042万
 $31,027/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -28140,7 +28140,7 @@
           <t>D | 616呎 (2房)
 $1817万
 $29,491/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -28148,7 +28148,7 @@
           <t>E | 570呎 (2房)
 $1725万
 $30,261/呎
-(26年-02月)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -28156,7 +28156,7 @@
           <t>F | 581呎 (2房)
 $1391万
 $23,946/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -28164,7 +28164,7 @@
           <t>G | 509呎 (2房)
 $1062万
 $20,870/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -28188,7 +28188,7 @@
           <t>C | 658呎 (3房)
 $2010万
 $30,550/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -28196,7 +28196,7 @@
           <t>D | 616呎 (2房)
 $1788万
 $29,028/呎
-(25年-05月)</t>
+(25年-05月-11日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -28204,7 +28204,7 @@
           <t>E | 571呎 (2房)
 $1701万
 $29,792/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -28212,7 +28212,7 @@
           <t>F | 582呎 (2房)
 $1289万
 $22,154/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -28220,7 +28220,7 @@
           <t>G | 509呎 (2房)
 $1048万
 $20,580/呎
-(25年-03月)</t>
+(25年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -28244,7 +28244,7 @@
           <t>C | 658呎 (3房)
 $1999万
 $30,381/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -28252,7 +28252,7 @@
           <t>D | 616呎 (2房)
 $1778万
 $28,857/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -28260,7 +28260,7 @@
           <t>E | 571呎 (2房)
 $1694万
 $29,674/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -28268,7 +28268,7 @@
           <t>F | 582呎 (2房)
 $1284万
 $22,065/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -28276,7 +28276,7 @@
           <t>G | 509呎 (2房)
 $1043万
 $20,498/呎
-(25年-02月)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
     </row>
@@ -28291,7 +28291,7 @@
           <t>A | 853呎 (3房)
 $3444万
 $40,375/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -28300,7 +28300,7 @@
           <t>C | 659呎 (3房)
 $1988万
 $30,161/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -28308,7 +28308,7 @@
           <t>D | 616呎 (2房)
 $1766万
 $28,662/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -28316,7 +28316,7 @@
           <t>E | 571呎 (2房)
 $1796万
 $31,450/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -28324,7 +28324,7 @@
           <t>F | 505呎 (2房)
 $1279万
 $25,329/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -28332,7 +28332,7 @@
           <t>G | 509呎 (2房)
 $1039万
 $20,418/呎
-(25年-02月)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -28356,7 +28356,7 @@
           <t>C | 658呎 (3房)
 $1988万
 $30,207/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -28364,7 +28364,7 @@
           <t>D | 616呎 (2房)
 $1766万
 $28,662/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -28372,7 +28372,7 @@
           <t>E | 571呎 (2房)
 $1680万
 $29,425/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -28380,7 +28380,7 @@
           <t>F | 582呎 (2房)
 $1279万
 $21,978/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -28388,7 +28388,7 @@
           <t>G | 509呎 (2房)
 $1039万
 $20,418/呎
-(25年-02月)</t>
+(25年-02月-23日)</t>
         </is>
       </c>
     </row>
@@ -28412,7 +28412,7 @@
           <t>C | 661呎 (3房)
 $2074万
 $31,378/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -28420,7 +28420,7 @@
           <t>D | 613呎 (2房)
 $1715万
 $27,981/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -28428,7 +28428,7 @@
           <t>E | 571呎 (2房)
 $1667万
 $29,193/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -28436,7 +28436,7 @@
           <t>F | 582呎 (2房)
 $1269万
 $21,804/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -28444,7 +28444,7 @@
           <t>G | 509呎 (2房)
 $1031万
 $20,256/呎
-(25年-03月)</t>
+(25年-03月-05日)</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
           <t>A | 853呎 (3房)
 $3246万
 $38,060/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -28468,7 +28468,7 @@
           <t>C | 661呎 (3房)
 $1948万
 $29,469/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -28476,7 +28476,7 @@
           <t>D | 613呎 (2房)
 $1689万
 $27,561/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -28484,7 +28484,7 @@
           <t>E | 571呎 (2房)
 $1660万
 $29,076/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -28492,7 +28492,7 @@
           <t>F | 582呎 (2房)
 $1264万
 $21,715/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -28500,7 +28500,7 @@
           <t>G | 509呎 (2房)
 $1053万
 $20,692/呎
-(25年-02月)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
     </row>
@@ -28515,7 +28515,7 @@
           <t>A | 853呎 (3房)
 $3030万
 $35,518/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
@@ -28524,7 +28524,7 @@
           <t>C | 661呎 (3房)
 $1889万
 $28,571/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -28532,7 +28532,7 @@
           <t>D | 613呎 (2房)
 $1680万
 $27,399/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -28540,7 +28540,7 @@
           <t>E | 570呎 (2房)
 $1654万
 $29,012/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -28548,7 +28548,7 @@
           <t>F | 582呎 (2房)
 $1259万
 $21,628/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -28556,7 +28556,7 @@
           <t>G | 509呎 (2房)
 $1049万
 $20,608/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -28571,7 +28571,7 @@
           <t>A | 853呎 (3房)
 $3009万
 $35,271/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -28580,7 +28580,7 @@
           <t>C | 661呎 (3房)
 $1878万
 $28,413/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -28588,7 +28588,7 @@
           <t>D | 613呎 (2房)
 $1670万
 $27,236/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -28596,7 +28596,7 @@
           <t>E | 571呎 (2房)
 $1647万
 $28,845/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -28604,7 +28604,7 @@
           <t>F | 582呎 (2房)
 $1254万
 $21,544/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -28612,7 +28612,7 @@
           <t>G | 509呎 (2房)
 $1019万
 $20,012/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
           <t>A | 853呎 (3房)
 $2988万
 $35,026/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -28636,7 +28636,7 @@
           <t>C | 661呎 (3房)
 $1868万
 $28,254/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -28644,7 +28644,7 @@
           <t>D | 613呎 (2房)
 $1669万
 $27,228/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -28652,7 +28652,7 @@
           <t>E | 571呎 (2房)
 $1640万
 $28,730/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -28660,7 +28660,7 @@
           <t>F | 582呎 (2房)
 $1249万
 $21,458/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -28668,7 +28668,7 @@
           <t>G | 509呎 (2房)
 $1015万
 $19,934/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
     </row>
@@ -28683,7 +28683,7 @@
           <t>A | 853呎 (3房)
 $3182万
 $37,300/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr"/>
@@ -28692,7 +28692,7 @@
           <t>C | 661呎 (3房)
 $1857万
 $28,097/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -28700,7 +28700,7 @@
           <t>D | 613呎 (2房)
 $1659万
 $27,067/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -28708,7 +28708,7 @@
           <t>E | 570呎 (2房)
 $1634万
 $28,666/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -28716,7 +28716,7 @@
           <t>F | 582呎 (2房)
 $1244万
 $21,372/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -28724,7 +28724,7 @@
           <t>G | 509呎 (2房)
 $1011万
 $19,854/呎
-(25年-02月)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -28739,7 +28739,7 @@
           <t>A | 853呎 (3房)
 $3224万
 $37,801/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr"/>
@@ -28748,7 +28748,7 @@
           <t>C | 661呎 (3房)
 $1847万
 $27,940/呎
-(25年-05月)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -28756,7 +28756,7 @@
           <t>D | 613呎 (2房)
 $1649万
 $26,908/呎
-(25年-02月)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -28764,7 +28764,7 @@
           <t>E | 571呎 (2房)
 $1627万
 $28,502/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -28772,7 +28772,7 @@
           <t>F | 582呎 (2房)
 $1239万
 $21,287/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -28780,7 +28780,7 @@
           <t>G | 509呎 (2房)
 $1007万
 $19,776/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
     </row>
@@ -28795,7 +28795,7 @@
           <t>A | 853呎 (3房)
 $3199万
 $37,501/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr"/>
@@ -28804,7 +28804,7 @@
           <t>C | 661呎 (3房)
 $1954万
 $29,565/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -28812,7 +28812,7 @@
           <t>D | 613呎 (2房)
 $1640万
 $26,749/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -28820,7 +28820,7 @@
           <t>E | 571呎 (2房)
 $1651万
 $28,908/呎
-(24年-05月)</t>
+(24年-05月-12日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -28828,7 +28828,7 @@
           <t>F | 582呎 (2房)
 $1234万
 $21,202/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -28836,7 +28836,7 @@
           <t>G | 509呎 (2房)
 $1003万
 $19,696/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -28860,7 +28860,7 @@
           <t>C | 661呎 (3房)
 $1837万
 $27,784/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -28868,7 +28868,7 @@
           <t>D | 613呎 (2房)
 $1640万
 $26,749/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -28876,7 +28876,7 @@
           <t>E | 571呎 (2房)
 $1621万
 $28,388/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -28884,7 +28884,7 @@
           <t>F | 582呎 (2房)
 $1234万
 $21,202/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -28892,7 +28892,7 @@
           <t>G | 509呎 (2房)
 $1003万
 $19,696/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -28916,7 +28916,7 @@
           <t>C | 661呎 (3房)
 $1817万
 $27,492/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -28924,7 +28924,7 @@
           <t>D | 613呎 (2房)
 $1622万
 $26,460/呎
-(25年-02月)</t>
+(25年-02月-23日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -28932,7 +28932,7 @@
           <t>E | 570呎 (2房)
 $1615万
 $28,336/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -28940,7 +28940,7 @@
           <t>F | 582呎 (2房)
 $1303万
 $22,383/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -28948,7 +28948,7 @@
           <t>G | 509呎 (2房)
 $995万
 $19,540/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
     </row>
@@ -28972,7 +28972,7 @@
           <t>C | 661呎 (3房)
 $1807万
 $27,339/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -28980,7 +28980,7 @@
           <t>D | 613呎 (2房)
 $1612万
 $26,305/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -28988,7 +28988,7 @@
           <t>E | 570呎 (2房)
 $1609万
 $28,224/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -28996,7 +28996,7 @@
           <t>F | 582呎 (2房)
 $1297万
 $22,293/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -29004,7 +29004,7 @@
           <t>G | 509呎 (2房)
 $991万
 $19,463/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -29019,7 +29019,7 @@
           <t>A | 517呎 (2房)
 $1428万
 $27,615/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -29027,7 +29027,7 @@
           <t>B | 520呎 (2房)
 $1450万
 $27,881/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29035,7 +29035,7 @@
           <t>C | 659呎 (3房)
 $1571万
 $23,840/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -29043,7 +29043,7 @@
           <t>D | 618呎 (2房)
 $1371万
 $22,186/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -29051,7 +29051,7 @@
           <t>E | 568呎 (2房)
 $1540万
 $27,114/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -29059,7 +29059,7 @@
           <t>F | 582呎 (2房)
 $1214万
 $20,867/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -29082,7 +29082,7 @@
           <t>A | 517呎 (2房)
 $1356万
 $26,226/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -29090,7 +29090,7 @@
           <t>B | 520呎 (2房)
 $1444万
 $27,770/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -29098,7 +29098,7 @@
           <t>C | 659呎 (3房)
 $1560万
 $23,675/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -29106,7 +29106,7 @@
           <t>D | 618呎 (2房)
 $1362万
 $22,043/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -29114,7 +29114,7 @@
           <t>E | 568呎 (2房)
 $1534万
 $27,005/呎
-(23年-08月)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -29122,7 +29122,7 @@
           <t>F | 582呎 (2房)
 $1210万
 $20,783/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -29130,7 +29130,7 @@
           <t>G | 403呎 (1房)
 $1080万
 $26,788/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -29145,7 +29145,7 @@
           <t>A | 517呎 (2房)
 $1416万
 $27,395/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -29153,7 +29153,7 @@
           <t>B | 520呎 (2房)
 $1371万
 $26,372/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -29161,7 +29161,7 @@
           <t>C | 659呎 (3房)
 $1549万
 $23,510/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -29169,7 +29169,7 @@
           <t>D | 618呎 (2房)
 $1353万
 $21,899/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -29177,7 +29177,7 @@
           <t>E | 567呎 (2房)
 $1556万
 $27,439/呎
-(24年-10月)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -29185,7 +29185,7 @@
           <t>F | 582呎 (2房)
 $1205万
 $20,701/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -29208,7 +29208,7 @@
           <t>A | 517呎 (2房)
 $1345万
 $26,016/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -29216,7 +29216,7 @@
           <t>B | 520呎 (2房)
 $1366万
 $26,267/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -29224,7 +29224,7 @@
           <t>C | 659呎 (3房)
 $1539万
 $23,347/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -29232,7 +29232,7 @@
           <t>D | 618呎 (2房)
 $1345万
 $21,758/呎
-(25年-02月)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -29240,7 +29240,7 @@
           <t>E | 568呎 (2房)
 $1522万
 $26,790/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -29248,7 +29248,7 @@
           <t>F | 582呎 (2房)
 $1200万
 $20,619/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -29271,7 +29271,7 @@
           <t>A | 517呎 (2房)
 $1340万
 $25,912/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -29279,7 +29279,7 @@
           <t>B | 518呎 (2房)
 $1360万
 $26,264/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -29287,7 +29287,7 @@
           <t>C | 659呎 (3房)
 $1528万
 $23,185/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -29295,7 +29295,7 @@
           <t>D | 618呎 (2房)
 $1336万
 $21,618/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -29303,7 +29303,7 @@
           <t>E | 568呎 (2房)
 $1516万
 $26,683/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -29311,7 +29311,7 @@
           <t>F | 582呎 (2房)
 $1195万
 $20,537/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -29334,7 +29334,7 @@
           <t>A | 517呎 (2房)
 $1561万
 $30,193/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -29342,7 +29342,7 @@
           <t>B | 520呎 (2房)
 $1360万
 $26,163/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -29350,7 +29350,7 @@
           <t>C | 659呎 (3房)
 $1528万
 $23,185/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -29358,7 +29358,7 @@
           <t>D | 618呎 (2房)
 $1370万
 $22,172/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -29366,7 +29366,7 @@
           <t>E | 568呎 (2房)
 $1516万
 $26,683/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -29374,7 +29374,7 @@
           <t>F | 582呎 (2房)
 $1195万
 $20,537/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -29397,7 +29397,7 @@
           <t>A | 517呎 (2房)
 $1329万
 $25,707/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -29405,7 +29405,7 @@
           <t>B | 520呎 (2房)
 $1350万
 $25,955/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -29413,7 +29413,7 @@
           <t>C | 659呎 (3房)
 $1507万
 $22,865/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -29421,7 +29421,7 @@
           <t>D | 618呎 (2房)
 $1319万
 $21,340/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -29429,7 +29429,7 @@
           <t>E | 568呎 (2房)
 $1504万
 $26,471/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -29437,7 +29437,7 @@
           <t>F | 582呎 (2房)
 $1186万
 $20,375/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H28" s="25" t="inlineStr">
@@ -29460,7 +29460,7 @@
           <t>A | 517呎 (2房)
 $1324万
 $25,604/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -29468,7 +29468,7 @@
           <t>B | 520呎 (2房)
 $1344万
 $25,851/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -29476,7 +29476,7 @@
           <t>C | 659呎 (3房)
 $1496万
 $22,707/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -29484,7 +29484,7 @@
           <t>D | 618呎 (2房)
 $1310万
 $21,203/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -29492,7 +29492,7 @@
           <t>E | 568呎 (2房)
 $1498万
 $26,366/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -29500,7 +29500,7 @@
           <t>F | 582呎 (2房)
 $1181万
 $20,293/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="H29" s="25" t="inlineStr">
@@ -29523,7 +29523,7 @@
           <t>A | 517呎 (2房)
 $1318万
 $25,503/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -29531,7 +29531,7 @@
           <t>B | 520呎 (2房)
 $1339万
 $25,748/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -29539,7 +29539,7 @@
           <t>C | 659呎 (3房)
 $1486万
 $22,549/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -29547,7 +29547,7 @@
           <t>D | 618呎 (2房)
 $1302万
 $21,065/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -29555,7 +29555,7 @@
           <t>E | 567呎 (2房)
 $1492万
 $26,307/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -29563,7 +29563,7 @@
           <t>F | 582呎 (2房)
 $1176万
 $20,213/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H30" s="25" t="inlineStr">
@@ -29586,7 +29586,7 @@
           <t>A | 517呎 (2房)
 $1313万
 $25,399/呎
-(25年-10月)</t>
+(25年-10月-26日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -29594,7 +29594,7 @@
           <t>B | 520呎 (2房)
 $1334万
 $25,646/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -29602,7 +29602,7 @@
           <t>C | 659呎 (3房)
 $1476万
 $22,392/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -29610,7 +29610,7 @@
           <t>D | 618呎 (2房)
 $1293万
 $20,929/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -29618,7 +29618,7 @@
           <t>E | 568呎 (2房)
 $1486万
 $26,156/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -29626,7 +29626,7 @@
           <t>F | 582呎 (2房)
 $1172万
 $20,133/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="H31" s="25" t="inlineStr">
@@ -29649,7 +29649,7 @@
           <t>A | 517呎 (2房)
 $1308万
 $25,300/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -29657,7 +29657,7 @@
           <t>B | 520呎 (2房)
 $1328万
 $25,543/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -29665,7 +29665,7 @@
           <t>C | 659呎 (3房)
 $1465万
 $22,237/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -29673,7 +29673,7 @@
           <t>D | 618呎 (2房)
 $1285万
 $20,794/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -29681,7 +29681,7 @@
           <t>E | 568呎 (2房)
 $1480万
 $26,052/呎
-(23年-07月)</t>
+(23年-07月-14日)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -29689,7 +29689,7 @@
           <t>F | 582呎 (2房)
 $1167万
 $20,052/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -29712,7 +29712,7 @@
           <t>A | 517呎 (2房)
 $1303万
 $25,198/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -29720,7 +29720,7 @@
           <t>B | 520呎 (2房)
 $1323万
 $25,442/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -29728,7 +29728,7 @@
           <t>C | 659呎 (3房)
 $1455万
 $22,083/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -29736,7 +29736,7 @@
           <t>D | 618呎 (2房)
 $1277万
 $20,659/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -29744,7 +29744,7 @@
           <t>E | 568呎 (2房)
 $1474万
 $25,948/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -29752,7 +29752,7 @@
           <t>F | 582呎 (2房)
 $1162万
 $19,972/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -29775,7 +29775,7 @@
           <t>A | 517呎 (2房)
 $1298万
 $25,098/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -29783,7 +29783,7 @@
           <t>B | 520呎 (2房)
 $1382万
 $26,576/呎
-(23年-08月)</t>
+(23年-08月-09日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -29791,7 +29791,7 @@
           <t>C | 659呎 (3房)
 $1445万
 $21,928/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -29799,7 +29799,7 @@
           <t>D | 618呎 (2房)
 $1269万
 $20,526/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -29807,7 +29807,7 @@
           <t>E | 567呎 (2房)
 $1603万
 $28,273/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -29815,7 +29815,7 @@
           <t>F | 582呎 (2房)
 $1158万
 $19,891/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -29838,7 +29838,7 @@
           <t>A | 517呎 (2房)
 $1298万
 $25,098/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -29846,7 +29846,7 @@
           <t>B | 520呎 (2房)
 $1318万
 $25,340/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -29854,7 +29854,7 @@
           <t>C | 659呎 (3房)
 $1445万
 $21,928/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -29862,7 +29862,7 @@
           <t>D | 618呎 (2房)
 $1269万
 $20,526/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -29870,7 +29870,7 @@
           <t>E | 568呎 (2房)
 $1468万
 $25,845/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -29878,7 +29878,7 @@
           <t>F | 582呎 (2房)
 $1158万
 $19,891/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -29901,7 +29901,7 @@
           <t>A | 517呎 (2房)
 $1287万
 $24,898/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -29909,7 +29909,7 @@
           <t>B | 520呎 (2房)
 $1371万
 $26,364/呎
-(23年-08月)</t>
+(23年-08月-06日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -29917,7 +29917,7 @@
           <t>C | 659呎 (3房)
 $1425万
 $21,625/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -29925,7 +29925,7 @@
           <t>D | 618呎 (2房)
 $1284万
 $20,782/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -29933,7 +29933,7 @@
           <t>E | 567呎 (2房)
 $1590万
 $28,049/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -29941,7 +29941,7 @@
           <t>F | 581呎 (2房)
 $1148万
 $19,767/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -29964,7 +29964,7 @@
           <t>A | 517呎 (2房)
 $1282万
 $24,800/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -29972,7 +29972,7 @@
           <t>B | 520呎 (2房)
 $1302万
 $25,038/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -29980,7 +29980,7 @@
           <t>C | 659呎 (3房)
 $1415万
 $21,474/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -29988,7 +29988,7 @@
           <t>D | 618呎 (2房)
 $1244万
 $20,132/呎
-(25年-02月)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -29996,7 +29996,7 @@
           <t>E | 568呎 (2房)
 $1451万
 $25,538/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -30004,7 +30004,7 @@
           <t>F | 582呎 (2房)
 $1144万
 $19,654/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -30245,7 +30245,7 @@
           <t>A | 915呎 (3房)
 $3653万
 $39,919/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -30253,7 +30253,7 @@
           <t>B | 678呎 (2房)
 $2219万
 $32,722/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -30261,7 +30261,7 @@
           <t>C | 861呎 (3房)
 $3547万
 $41,201/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -30269,7 +30269,7 @@
           <t>D | 535呎 (2房)
 $1231万
 $23,014/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -30277,7 +30277,7 @@
           <t>E | 486呎 (2房)
 $1092万
 $22,468/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -30285,7 +30285,7 @@
           <t>F | 505呎 (2房)
 $1119万
 $22,160/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr"/>
@@ -30301,7 +30301,7 @@
           <t>A | 915呎 (3房)
 $3561万
 $38,919/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -30309,7 +30309,7 @@
           <t>B | 678呎 (2房)
 $2182万
 $32,176/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -30317,7 +30317,7 @@
           <t>C | 861呎 (3房)
 $3033万
 $35,226/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -30325,7 +30325,7 @@
           <t>D | 535呎 (2房)
 $1214万
 $22,696/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -30333,7 +30333,7 @@
           <t>E | 485呎 (2房)
 $1077万
 $22,202/呎
-(25年-05月)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -30341,7 +30341,7 @@
           <t>F | 505呎 (2房)
 $1104万
 $21,852/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr"/>
@@ -30357,7 +30357,7 @@
           <t>A | 915呎 (3房)
 $3470万
 $37,919/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -30365,7 +30365,7 @@
           <t>B | 678呎 (2房)
 $2166万
 $31,951/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -30373,7 +30373,7 @@
           <t>C | 861呎 (3房)
 $3010万
 $34,965/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -30381,7 +30381,7 @@
           <t>D | 535呎 (2房)
 $1209万
 $22,605/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -30389,7 +30389,7 @@
           <t>E | 486呎 (2房)
 $1073万
 $22,070/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -30397,7 +30397,7 @@
           <t>F | 505呎 (2房)
 $1099万
 $21,764/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
           <t>A | 915呎 (3房)
 $3378万
 $36,919/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -30421,7 +30421,7 @@
           <t>B | 678呎 (2房)
 $2151万
 $31,729/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -30429,7 +30429,7 @@
           <t>C | 861呎 (3房)
 $2869万
 $33,321/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -30437,7 +30437,7 @@
           <t>D | 535呎 (2房)
 $1205万
 $22,515/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -30445,7 +30445,7 @@
           <t>E | 486呎 (2房)
 $1068万
 $21,980/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -30453,7 +30453,7 @@
           <t>F | 505呎 (2房)
 $1095万
 $21,678/呎
-(25年-06月)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr"/>
@@ -30469,7 +30469,7 @@
           <t>A | 915呎 (3房)
 $3378万
 $36,919/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -30477,7 +30477,7 @@
           <t>B | 678呎 (2房)
 $2151万
 $31,729/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -30485,7 +30485,7 @@
           <t>C | 861呎 (3房)
 $2869万
 $33,321/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -30493,7 +30493,7 @@
           <t>D | 535呎 (2房)
 $1205万
 $22,515/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -30501,7 +30501,7 @@
           <t>E | 486呎 (2房)
 $1068万
 $21,980/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -30509,7 +30509,7 @@
           <t>F | 505呎 (2房)
 $1095万
 $21,678/呎
-(25年-04月)</t>
+(25年-04月-13日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr"/>
@@ -30525,7 +30525,7 @@
           <t>A | 915呎 (3房)
 $3295万
 $36,011/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -30533,7 +30533,7 @@
           <t>B | 678呎 (2房)
 $2122万
 $31,291/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -30541,7 +30541,7 @@
           <t>C | 861呎 (3房)
 $2923万
 $33,951/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -30549,7 +30549,7 @@
           <t>D | 535呎 (2房)
 $1195万
 $22,337/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -30557,7 +30557,7 @@
           <t>E | 486呎 (2房)
 $1060万
 $21,805/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -30565,7 +30565,7 @@
           <t>F | 505呎 (2房)
 $1086万
 $21,507/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr"/>
@@ -30581,7 +30581,7 @@
           <t>A | 915呎 (3房)
 $3411万
 $37,279/呎
-(23年-12月)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -30589,7 +30589,7 @@
           <t>B | 678呎 (2房)
 $2138万
 $31,538/呎
-(23年-08月)</t>
+(23年-08月-06日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -30597,7 +30597,7 @@
           <t>C | 861呎 (3房)
 $2843万
 $33,021/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -30605,7 +30605,7 @@
           <t>D | 535呎 (2房)
 $1190万
 $22,248/呎
-(25年-02月)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -30613,7 +30613,7 @@
           <t>E | 485呎 (2房)
 $1056万
 $21,763/呎
-(25年-03月)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -30621,7 +30621,7 @@
           <t>F | 505呎 (2房)
 $1082万
 $21,422/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr"/>
@@ -30637,7 +30637,7 @@
           <t>A | 915呎 (3房)
 $3388万
 $37,027/呎
-(23年-09月)</t>
+(23年-09月-18日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -30645,7 +30645,7 @@
           <t>B | 678呎 (2房)
 $2085万
 $30,757/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -30653,7 +30653,7 @@
           <t>C | 861呎 (3房)
 $2883万
 $33,482/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -30661,7 +30661,7 @@
           <t>D | 535呎 (2房)
 $1186万
 $22,161/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -30669,7 +30669,7 @@
           <t>E | 486呎 (2房)
 $1051万
 $21,633/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -30677,7 +30677,7 @@
           <t>F | 505呎 (2房)
 $1077万
 $21,335/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr"/>
@@ -30693,7 +30693,7 @@
           <t>A | 915呎 (3房)
 $3180万
 $34,754/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -30701,7 +30701,7 @@
           <t>B | 678呎 (2房)
 $2071万
 $30,543/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -30709,7 +30709,7 @@
           <t>C | 861呎 (3房)
 $2863万
 $33,249/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -30717,7 +30717,7 @@
           <t>D | 535呎 (2房)
 $1181万
 $22,072/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -30725,7 +30725,7 @@
           <t>E | 486呎 (2房)
 $1047万
 $21,546/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -30733,7 +30733,7 @@
           <t>F | 505呎 (2房)
 $1073万
 $21,250/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
           <t>A | 915呎 (3房)
 $3157万
 $34,503/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -30757,7 +30757,7 @@
           <t>B | 678呎 (2房)
 $2056万
 $30,332/呎
-(23年-07月)</t>
+(23年-07月-14日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -30765,7 +30765,7 @@
           <t>C | 861呎 (3房)
 $2843万
 $33,017/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -30773,7 +30773,7 @@
           <t>D | 535呎 (2房)
 $1176万
 $21,984/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -30781,7 +30781,7 @@
           <t>E | 486呎 (2房)
 $1043万
 $21,461/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -30789,7 +30789,7 @@
           <t>F | 505呎 (2房)
 $1069万
 $21,164/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr"/>
@@ -30805,7 +30805,7 @@
           <t>A | 915呎 (3房)
 $3134万
 $34,251/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -30813,7 +30813,7 @@
           <t>B | 678呎 (2房)
 $2042万
 $30,121/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -30821,7 +30821,7 @@
           <t>C | 861呎 (3房)
 $2998万
 $34,816/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -30829,7 +30829,7 @@
           <t>D | 535呎 (2房)
 $1171万
 $21,896/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -30837,7 +30837,7 @@
           <t>E | 486呎 (2房)
 $1039万
 $21,375/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -30845,7 +30845,7 @@
           <t>F | 505呎 (2房)
 $1065万
 $21,080/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr"/>
@@ -30861,7 +30861,7 @@
           <t>A | 915呎 (3房)
 $3111万
 $34,000/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -30869,7 +30869,7 @@
           <t>B | 678呎 (2房)
 $2127万
 $31,372/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -30877,7 +30877,7 @@
           <t>C | 861呎 (3房)
 $3080万
 $35,776/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -30885,7 +30885,7 @@
           <t>D | 535呎 (2房)
 $1167万
 $21,810/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -30893,7 +30893,7 @@
           <t>E | 486呎 (2房)
 $1035万
 $21,290/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -30901,7 +30901,7 @@
           <t>F | 505呎 (2房)
 $1060万
 $20,997/呎
-(25年-04月)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
           <t>A | 915呎 (3房)
 $3088万
 $33,749/呎
-(23年-10月)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -30925,7 +30925,7 @@
           <t>B | 678呎 (2房)
 $2051万
 $30,249/呎
-(23年-08月)</t>
+(23年-08月-15日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -30933,7 +30933,7 @@
           <t>C | 861呎 (3房)
 $3059万
 $35,533/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -30941,7 +30941,7 @@
           <t>D | 535呎 (2房)
 $1162万
 $21,722/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -30949,7 +30949,7 @@
           <t>E | 486呎 (2房)
 $1031万
 $21,205/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -30957,7 +30957,7 @@
           <t>F | 505呎 (2房)
 $1056万
 $20,913/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr"/>
@@ -30973,7 +30973,7 @@
           <t>A | 915呎 (3房)
 $3065万
 $33,497/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -30981,7 +30981,7 @@
           <t>B | 678呎 (2房)
 $1994万
 $29,410/呎
-(23年-08月)</t>
+(23年-08月-10日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -30997,7 +30997,7 @@
           <t>D | 535呎 (2房)
 $1162万
 $21,722/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -31005,7 +31005,7 @@
           <t>E | 486呎 (2房)
 $1031万
 $21,205/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -31013,7 +31013,7 @@
           <t>F | 505呎 (2房)
 $1056万
 $20,913/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr"/>
@@ -31029,7 +31029,7 @@
           <t>A | 915呎 (3房)
 $3088万
 $33,746/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -31037,7 +31037,7 @@
           <t>B | 678呎 (2房)
 $1942万
 $28,641/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -31053,7 +31053,7 @@
           <t>D | 535呎 (2房)
 $1153万
 $21,550/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -31061,7 +31061,7 @@
           <t>E | 486呎 (2房)
 $1022万
 $21,036/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -31069,7 +31069,7 @@
           <t>F | 505呎 (2房)
 $1048万
 $20,748/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
           <t>A | 915呎 (3房)
 $3065万
 $33,495/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -31093,7 +31093,7 @@
           <t>B | 678呎 (2房)
 $1904万
 $28,080/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -31101,7 +31101,7 @@
           <t>C | 861呎 (3房)
 $3014万
 $35,000/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -31109,7 +31109,7 @@
           <t>D | 535呎 (2房)
 $1148万
 $21,464/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -31117,7 +31117,7 @@
           <t>E | 486呎 (2房)
 $1018万
 $20,951/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -31125,7 +31125,7 @@
           <t>F | 505呎 (2房)
 $1044万
 $20,665/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr"/>
@@ -31141,7 +31141,7 @@
           <t>A | 914呎 (3房)
 $3027万
 $33,120/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -31149,7 +31149,7 @@
           <t>B | 680呎 (2房)
 $1882万
 $27,681/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -31157,7 +31157,7 @@
           <t>C | 629呎 (2房)
 $1452万
 $23,086/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -31165,7 +31165,7 @@
           <t>D | 535呎 (2房)
 $1144万
 $21,376/呎
-(25年-02月)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -31173,7 +31173,7 @@
           <t>E | 488呎 (2房)
 $1014万
 $20,782/呎
-(25年-03月)</t>
+(25年-03月-16日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -31204,7 +31204,7 @@
           <t>A | 914呎 (3房)
 $3044万
 $33,299/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -31212,7 +31212,7 @@
           <t>B | 680呎 (2房)
 $1907万
 $28,048/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -31220,7 +31220,7 @@
           <t>C | 629呎 (2房)
 $1445万
 $22,971/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -31228,7 +31228,7 @@
           <t>D | 535呎 (2房)
 $1139万
 $21,292/呎
-(25年-02月)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -31236,7 +31236,7 @@
           <t>E | 488呎 (2房)
 $1010万
 $20,700/呎
-(25年-03月)</t>
+(25年-03月-02日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -31267,7 +31267,7 @@
           <t>A | 914呎 (3房)
 $3075万
 $33,639/呎
-(23年-07月)</t>
+(23年-07月-14日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -31275,7 +31275,7 @@
           <t>B | 680呎 (2房)
 $1955万
 $28,743/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -31283,7 +31283,7 @@
           <t>C | 629呎 (2房)
 $1438万
 $22,856/呎
-(25年-05月)</t>
+(25年-05月-11日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -31291,7 +31291,7 @@
           <t>D | 535呎 (2房)
 $1135万
 $21,207/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -31299,7 +31299,7 @@
           <t>E | 488呎 (2房)
 $1006万
 $20,616/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -31330,7 +31330,7 @@
           <t>A | 914呎 (3房)
 $3053万
 $33,405/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -31338,7 +31338,7 @@
           <t>B | 680呎 (2房)
 $1854万
 $27,270/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -31346,7 +31346,7 @@
           <t>C | 629呎 (2房)
 $1431万
 $22,743/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -31354,7 +31354,7 @@
           <t>D | 535呎 (2房)
 $1130万
 $21,123/呎
-(25年-02月)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -31362,7 +31362,7 @@
           <t>E | 488呎 (2房)
 $1002万
 $20,536/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -31370,7 +31370,7 @@
           <t>F | 394呎 (1房)
 $1056万
 $26,810/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -31393,7 +31393,7 @@
           <t>A | 914呎 (3房)
 $2891万
 $31,630/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -31401,7 +31401,7 @@
           <t>B | 680呎 (2房)
 $1879万
 $27,630/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -31409,7 +31409,7 @@
           <t>C | 629呎 (2房)
 $1423万
 $22,629/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -31417,7 +31417,7 @@
           <t>D | 535呎 (2房)
 $1126万
 $21,038/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -31425,7 +31425,7 @@
           <t>E | 488呎 (2房)
 $998万
 $20,453/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -31456,7 +31456,7 @@
           <t>A | 914呎 (3房)
 $2891万
 $31,630/呎
-(23年-08月)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -31464,7 +31464,7 @@
           <t>B | 680呎 (2房)
 $1845万
 $27,134/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -31472,7 +31472,7 @@
           <t>C | 629呎 (2房)
 $1423万
 $22,629/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -31480,7 +31480,7 @@
           <t>D | 535呎 (2房)
 $1126万
 $21,038/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -31488,7 +31488,7 @@
           <t>E | 488呎 (2房)
 $998万
 $20,453/呎
-(25年-02月)</t>
+(25年-02月-24日)</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
@@ -31519,7 +31519,7 @@
           <t>A | 914呎 (3房)
 $2903万
 $31,764/呎
-(23年-08月)</t>
+(23年-08月-10日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -31527,7 +31527,7 @@
           <t>B | 680呎 (2房)
 $1827万
 $26,865/呎
-(23年-08月)</t>
+(23年-08月-10日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -31535,7 +31535,7 @@
           <t>C | 629呎 (2房)
 $1409万
 $22,406/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -31543,7 +31543,7 @@
           <t>D | 535呎 (2房)
 $1117万
 $20,872/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -31551,7 +31551,7 @@
           <t>E | 488呎 (2房)
 $990万
 $20,293/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
@@ -31582,7 +31582,7 @@
           <t>A | 914呎 (3房)
 $2883万
 $31,544/呎
-(23年-08月)</t>
+(23年-08月-06日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -31590,7 +31590,7 @@
           <t>B | 680呎 (2房)
 $1818万
 $26,731/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -31598,7 +31598,7 @@
           <t>C | 629呎 (2房)
 $1402万
 $22,294/呎
-(25年-05月)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -31606,7 +31606,7 @@
           <t>D | 535呎 (2房)
 $1112万
 $20,789/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -31614,7 +31614,7 @@
           <t>E | 488呎 (2房)
 $986万
 $20,210/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
@@ -31645,7 +31645,7 @@
           <t>A | 914呎 (3房)
 $3288万
 $35,974/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -31653,7 +31653,7 @@
           <t>B | 680呎 (2房)
 $1897万
 $27,896/呎
-(23年-10月)</t>
+(23年-10月-09日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -31661,7 +31661,7 @@
           <t>C | 629呎 (2房)
 $1395万
 $22,184/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -31669,7 +31669,7 @@
           <t>D | 535呎 (2房)
 $1108万
 $20,706/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -31677,7 +31677,7 @@
           <t>E | 488呎 (2房)
 $982万
 $20,130/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
@@ -31708,7 +31708,7 @@
           <t>A | 914呎 (3房)
 $2928万
 $32,037/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -31716,7 +31716,7 @@
           <t>B | 680呎 (2房)
 $1888万
 $27,758/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -31724,7 +31724,7 @@
           <t>C | 629呎 (2房)
 $1388万
 $22,073/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -31732,7 +31732,7 @@
           <t>D | 535呎 (2房)
 $1103万
 $20,624/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -31740,7 +31740,7 @@
           <t>E | 488呎 (2房)
 $978万
 $20,047/呎
-(25年-02月)</t>
+(25年-02月-23日)</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
@@ -31771,7 +31771,7 @@
           <t>A | 914呎 (3房)
 $2908万
 $31,815/呎
-(23年-08月)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -31779,7 +31779,7 @@
           <t>B | 680呎 (2房)
 $1878万
 $27,620/呎
-(23年-08月)</t>
+(23年-08月-09日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -31787,7 +31787,7 @@
           <t>C | 629呎 (2房)
 $1381万
 $21,963/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -31795,7 +31795,7 @@
           <t>D | 535呎 (2房)
 $1099万
 $20,541/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -31803,7 +31803,7 @@
           <t>E | 488呎 (2房)
 $974万
 $19,968/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
@@ -31834,7 +31834,7 @@
           <t>A | 914呎 (3房)
 $2753万
 $30,124/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -31842,7 +31842,7 @@
           <t>B | 680呎 (2房)
 $1782万
 $26,204/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -31850,7 +31850,7 @@
           <t>C | 629呎 (2房)
 $1375万
 $21,854/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -31858,7 +31858,7 @@
           <t>D | 535呎 (2房)
 $1094万
 $20,458/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -31866,7 +31866,7 @@
           <t>E | 488呎 (2房)
 $971万
 $19,890/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -31897,7 +31897,7 @@
           <t>A | 914呎 (3房)
 $2868万
 $31,374/呎
-(23年-08月)</t>
+(23年-08月-08日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -31905,7 +31905,7 @@
           <t>B | 680呎 (2房)
 $1860万
 $27,346/呎
-(23年-08月)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -31913,7 +31913,7 @@
           <t>C | 629呎 (2房)
 $1368万
 $21,746/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -31921,7 +31921,7 @@
           <t>D | 535呎 (2房)
 $1090万
 $20,378/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -31929,7 +31929,7 @@
           <t>E | 488呎 (2房)
 $967万
 $19,810/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -31960,7 +31960,7 @@
           <t>A | 914呎 (3房)
 $2762万
 $30,216/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -31968,7 +31968,7 @@
           <t>B | 680呎 (2房)
 $1805万
 $26,551/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -31976,7 +31976,7 @@
           <t>C | 629呎 (2房)
 $1368万
 $21,746/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -31984,7 +31984,7 @@
           <t>D | 535呎 (2房)
 $1090万
 $20,378/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -31992,7 +31992,7 @@
           <t>E | 488呎 (2房)
 $967万
 $19,810/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -32023,7 +32023,7 @@
           <t>A | 914呎 (3房)
 $2762万
 $30,216/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -32031,7 +32031,7 @@
           <t>B | 680呎 (2房)
 $1788万
 $26,288/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -32039,7 +32039,7 @@
           <t>C | 629呎 (2房)
 $1354万
 $21,530/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -32047,7 +32047,7 @@
           <t>D | 535呎 (2房)
 $1082万
 $20,216/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -32055,7 +32055,7 @@
           <t>E | 488呎 (2房)
 $959万
 $19,652/呎
-(25年-02月)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -32086,7 +32086,7 @@
           <t>A | 914呎 (3房)
 $2678万
 $29,298/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -32094,7 +32094,7 @@
           <t>B | 680呎 (2房)
 $1747万
 $25,688/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -32102,7 +32102,7 @@
           <t>C | 629呎 (2房)
 $1347万
 $21,422/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -32110,7 +32110,7 @@
           <t>D | 535呎 (2房)
 $1077万
 $20,136/呎
-(25年-02月)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -32118,7 +32118,7 @@
           <t>E | 488呎 (2房)
 $955万
 $19,574/呎
-(25年-02月)</t>
+(25年-02月-23日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
